--- a/outputs/metrics/sequence_window_validation_metrics.xlsx
+++ b/outputs/metrics/sequence_window_validation_metrics.xlsx
@@ -485,34 +485,34 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.7166900420757363</v>
+        <v>0.7194950911640954</v>
       </c>
       <c r="B2" t="n">
-        <v>0.4768518518518519</v>
+        <v>0.7129629629629629</v>
       </c>
       <c r="C2" t="n">
-        <v>0.4635416666666667</v>
+        <v>0.4726027397260274</v>
       </c>
       <c r="D2" t="n">
-        <v>0.5049019607843137</v>
+        <v>0.6062992125984252</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3377049180327869</v>
+        <v>0.4350282485875706</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7705119606528058</v>
+        <v>0.7756818689917282</v>
       </c>
       <c r="G2" t="n">
-        <v>408</v>
+        <v>359</v>
       </c>
       <c r="H2" t="n">
-        <v>89</v>
+        <v>138</v>
       </c>
       <c r="I2" t="n">
-        <v>113</v>
+        <v>62</v>
       </c>
       <c r="J2" t="n">
-        <v>103</v>
+        <v>154</v>
       </c>
       <c r="K2" t="n">
         <v>0.5</v>
@@ -530,34 +530,34 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.6339410939691444</v>
+        <v>0.6732117812061711</v>
       </c>
       <c r="B3" t="n">
-        <v>0.8611111111111112</v>
+        <v>0.7685185185185185</v>
       </c>
       <c r="C3" t="n">
-        <v>0.5539568345323741</v>
+        <v>0.5243553008595988</v>
       </c>
       <c r="D3" t="n">
-        <v>0.5876777251184834</v>
+        <v>0.5876106194690266</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4161073825503356</v>
+        <v>0.4160401002506265</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7493293091884641</v>
+        <v>0.7575266413294582</v>
       </c>
       <c r="G3" t="n">
-        <v>266</v>
+        <v>314</v>
       </c>
       <c r="H3" t="n">
-        <v>231</v>
+        <v>183</v>
       </c>
       <c r="I3" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="J3" t="n">
-        <v>186</v>
+        <v>166</v>
       </c>
       <c r="K3" t="n">
         <v>0.5</v>
@@ -575,34 +575,34 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.6718092566619915</v>
+        <v>0.6760168302945302</v>
       </c>
       <c r="B4" t="n">
-        <v>0.8287037037037037</v>
+        <v>0.6944444444444444</v>
       </c>
       <c r="C4" t="n">
-        <v>0.523936170212766</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6047297297297297</v>
+        <v>0.5649717514124294</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4334140435835351</v>
+        <v>0.3937007874015748</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7664319248826291</v>
+        <v>0.7476153215589836</v>
       </c>
       <c r="G4" t="n">
-        <v>300</v>
+        <v>332</v>
       </c>
       <c r="H4" t="n">
-        <v>197</v>
+        <v>165</v>
       </c>
       <c r="I4" t="n">
-        <v>37</v>
+        <v>66</v>
       </c>
       <c r="J4" t="n">
-        <v>179</v>
+        <v>150</v>
       </c>
       <c r="K4" t="n">
         <v>0.5</v>
@@ -620,34 +620,34 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0.6942496493688639</v>
+        <v>0.7110799438990182</v>
       </c>
       <c r="B5" t="n">
-        <v>0.5555555555555556</v>
+        <v>0.6481481481481481</v>
       </c>
       <c r="C5" t="n">
-        <v>0.5041322314049587</v>
+        <v>0.4814814814814815</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5240174672489083</v>
+        <v>0.5761316872427984</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3550295857988165</v>
+        <v>0.4046242774566474</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7564460839108725</v>
+        <v>0.769217154780535</v>
       </c>
       <c r="G5" t="n">
-        <v>375</v>
+        <v>367</v>
       </c>
       <c r="H5" t="n">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="I5" t="n">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="J5" t="n">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="K5" t="n">
         <v>0.5</v>
@@ -665,34 +665,34 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>0.6437587657784011</v>
+        <v>0.5357643758765779</v>
       </c>
       <c r="B6" t="n">
-        <v>0.8518518518518519</v>
+        <v>0.9537037037037037</v>
       </c>
       <c r="C6" t="n">
-        <v>0.5467980295566502</v>
+        <v>0.6091081593927894</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5916398713826366</v>
+        <v>0.5545087483176312</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4200913242009132</v>
+        <v>0.3836126629422719</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7536049631120052</v>
+        <v>0.7426037707727848</v>
       </c>
       <c r="G6" t="n">
-        <v>275</v>
+        <v>176</v>
       </c>
       <c r="H6" t="n">
-        <v>222</v>
+        <v>321</v>
       </c>
       <c r="I6" t="n">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="J6" t="n">
-        <v>184</v>
+        <v>206</v>
       </c>
       <c r="K6" t="n">
         <v>0.5</v>
@@ -710,34 +710,34 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0.6591865357643759</v>
+        <v>0.6619915848527349</v>
       </c>
       <c r="B7" t="n">
-        <v>0.7638888888888888</v>
+        <v>0.7824074074074074</v>
       </c>
       <c r="C7" t="n">
-        <v>0.5378151260504201</v>
+        <v>0.5344352617079889</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5759162303664922</v>
+        <v>0.5837651122625216</v>
       </c>
       <c r="E7" t="n">
-        <v>0.4044117647058824</v>
+        <v>0.4121951219512195</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7531485207541545</v>
+        <v>0.7555052537446904</v>
       </c>
       <c r="G7" t="n">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="H7" t="n">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="I7" t="n">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="J7" t="n">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="K7" t="n">
         <v>0.5</v>
